--- a/r4-JoanneumResearch-PreNUDGE-AppData-sleep/all-profiles.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-sleep/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T13:56:00+00:00</t>
+    <t>2026-05-18T14:18:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-sleep/all-profiles.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-sleep/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T15:35:26+00:00</t>
+    <t>2026-05-28T10:55:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2791,10 +2791,10 @@
     <t>Questions or sub-groups nested beneath a question or group.</t>
   </si>
   <si>
-    <t>at-prenudge-sleep-observation</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/prenudge/appdata/r4/StructureDefinition/at-prenudge-sleep-observation</t>
+    <t>at-prenudge-sleep-duration-observation</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/prenudge/appdata/r4/StructureDefinition/at-prenudge-sleep-duration-observation</t>
   </si>
   <si>
     <t>AtPrenudgeObservationSleepDuration</t>
